--- a/week3/manual_gold/001282_三联锻造_gold.xlsx
+++ b/week3/manual_gold/001282_三联锻造_gold.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,16 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>数据来源类型</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -496,6 +506,11 @@
           <t>2004年1月，孙国奉、孙国敏、张松满共同出资设立三联有限，注册资本500万元，其中孙国奉出资175万元，占比35%</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,6 +547,11 @@
           <t>孙国敏出资162.5万元，占比32.5%</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -568,6 +588,11 @@
           <t>张松满出资162.5万元，占比32.5%</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -606,6 +631,11 @@
           <t>2018年11月，三联有限整体变更为股份公司，以经审计净资产折股8150万股</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -640,6 +670,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>2019年12月，三联合伙以现金1566万元认购新增注册资本348万元，每股价格4.50元</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>直接披露</t>
         </is>
       </c>
     </row>
@@ -654,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,6 +743,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>时点说明</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -752,6 +792,11 @@
           <t>设立时孙国奉出资175万元，占比35%</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -796,6 +841,11 @@
           <t>孙国敏出资162.5万元，占比32.5%</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -840,6 +890,11 @@
           <t>张松满出资162.5万元，占比32.5%</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -890,6 +945,11 @@
           <t>2018年11月整体变更为股份公司，以净资产折股8150万股</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -938,6 +998,11 @@
           <t>发行前孙国奉持股26.91%</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -986,6 +1051,11 @@
           <t>张一衡持股26.77%</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1034,6 +1104,11 @@
           <t>孙国敏持股26.77%</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1082,6 +1157,11 @@
           <t>高新同华持股13.53%</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1130,6 +1210,11 @@
           <t>三联合伙（员工持股平台）持股4.10%</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1176,6 +1261,11 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>孙仁豪持股1.92%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>IPO发行前的股权结构</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1457,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>转让类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1409,6 +1504,7 @@
           <t>翻遍了，发行人层面没找到股权转让（报告期前的转让这版招股书没收，详细在申报文件4-3里）</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
